--- a/VerveStacks_TJK_grids/SysSettings.xlsx
+++ b/VerveStacks_TJK_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F0144A-C4F2-45DE-ACC7-F7FC36E0F230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9829768D-4DF2-4AD3-A49E-C76BECEF97BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4171,7 +4171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4703F945-B102-487B-8EF6-3B34E18FB2F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52A12DB-8FAD-4125-B469-B18539C128DC}">
   <dimension ref="B3:H17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SysSettings.xlsx
+++ b/VerveStacks_TJK_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9829768D-4DF2-4AD3-A49E-C76BECEF97BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B105530-79B5-4BE4-808C-30698D8F4BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4171,7 +4171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52A12DB-8FAD-4125-B469-B18539C128DC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB875FF6-A005-4003-A8F4-B5CD29F499CB}">
   <dimension ref="B3:H17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SysSettings.xlsx
+++ b/VerveStacks_TJK_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B105530-79B5-4BE4-808C-30698D8F4BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39D6612-9C7A-4ADB-9411-4E458B14084B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4171,7 +4171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB875FF6-A005-4003-A8F4-B5CD29F499CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F533F158-C448-4B8C-B4E3-CD105039FCDF}">
   <dimension ref="B3:H17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_TJK_grids/SysSettings.xlsx
+++ b/VerveStacks_TJK_grids/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_TJK_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39D6612-9C7A-4ADB-9411-4E458B14084B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F074C4B-63D0-4432-A33A-02382CE854D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4171,7 +4171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F533F158-C448-4B8C-B4E3-CD105039FCDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9392D9A6-793E-4473-B357-B2E7E2F9E684}">
   <dimension ref="B3:H17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
